--- a/KOSPI PBR/엘라스틱PBR.xlsx
+++ b/KOSPI PBR/엘라스틱PBR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GSR\Desktop\Code\git_folder\KOSPI PBR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16BCD5BC-9B6D-4E66-8A25-724DEF02B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BB46B3-45E3-4972-98B2-186A0D084E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7875" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{FE350A5E-9074-4EB6-9444-23315B9183C7}"/>
+    <workbookView xWindow="3315" yWindow="2145" windowWidth="28800" windowHeight="15345" xr2:uid="{FE350A5E-9074-4EB6-9444-23315B9183C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>과거</t>
   </si>
@@ -279,6 +279,10 @@
       </rPr>
       <t>시그널 만들기</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>과거</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -401,17 +405,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -426,10 +430,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -439,6 +443,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -804,8 +811,8 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
-        <v>0</v>
+      <c r="B4" s="13" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>1</v>
